--- a/src/main/resources/product_list.xlsx
+++ b/src/main/resources/product_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Selenium\amazon-price-tracker\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B297130C-C861-48EF-B625-BF753313079C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B43AAC1-66A6-4D71-A697-44C87FD38DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F3389CCB-2CB4-42F7-8DFC-B512498D7A21}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ASIN</t>
   </si>
@@ -52,12 +52,6 @@
   </si>
   <si>
     <t>Cut shoe</t>
-  </si>
-  <si>
-    <t>B0H1R6YTDV</t>
-  </si>
-  <si>
-    <t>Anarkali Kurti</t>
   </si>
   <si>
     <t>B0FBGQPCJZ</t>
@@ -427,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E99F1D-8C67-4E2C-8CB7-9E8F1810907B}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.77734375" customWidth="1"/>
@@ -487,7 +481,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -498,7 +492,7 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -509,17 +503,6 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8">
         <v>4000</v>
       </c>
     </row>
